--- a/questionnaire_templates/037_introductory_questionnaire_sheet_graphics--questionnaire_templates.xlsx
+++ b/questionnaire_templates/037_introductory_questionnaire_sheet_graphics--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'web'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'web'}</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'web'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Web'}</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>web_choices</t>
+          <t>print_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'web'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'web'}</t>
+          <t>print</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>print_choices</t>
+          <t>video_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Print'}</t>
+          <t>video</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>print_choices</t>
+          <t>video_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'print'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>video_choices</t>
+          <t>work_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'video'}</t>
+          <t>logo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>video_choices</t>
+          <t>work_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>icon</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>video_choices</t>
+          <t>work_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>banner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'video'}</t>
+          <t>banner</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'logo'}</t>
+          <t>brochure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'logo'}</t>
+          <t>brochure</t>
         </is>
       </c>
     </row>
@@ -1301,505 +1301,369 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'logo'}</t>
+          <t>business_cards</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'logo'}</t>
+          <t>business cards</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>color_mode_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'icon'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'icon'}</t>
+          <t>color</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>color_mode_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'banner'}</t>
+          <t>grayscale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'banner'}</t>
+          <t>grayscale</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>format_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'banner'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'banner'}</t>
+          <t>portrait</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>format_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'brochure'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'brochure'}</t>
+          <t>landscape</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>format_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'business_cards'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'business_cards'}</t>
+          <t>square</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>color_mode_choices</t>
+          <t>orientation_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'color'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'color'}</t>
+          <t>portrait</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>color_mode_choices</t>
+          <t>orientation_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'grayscale'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'grayscale'}</t>
+          <t>landscape</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>format_choices</t>
+          <t>bleed_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'portrait'}</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'portrait'}</t>
+          <t>bleed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>format_choices</t>
+          <t>bleed_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'landscape'}</t>
+          <t>no_bleed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'landscape'}</t>
+          <t>no bleed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>format_choices</t>
+          <t>trim_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'square'}</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'square'}</t>
+          <t>bleed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>orientation_choices</t>
+          <t>trim_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'portrait'}</t>
+          <t>no_trim</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'portrait'}</t>
+          <t>no trim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>orientation_choices</t>
+          <t>finish_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'landscape'}</t>
+          <t>matte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'landscape'}</t>
+          <t>matte</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bleed_choices</t>
+          <t>finish_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'bleed'}</t>
+          <t>glossy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'bleed'}</t>
+          <t>glossy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bleed_choices</t>
+          <t>paper_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'no_bleed'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'no_bleed'}</t>
+          <t>card</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>trim_type_choices</t>
+          <t>paper_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'bleed'}</t>
+          <t>8pt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'bleed'}</t>
+          <t>8pt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>trim_type_choices</t>
+          <t>bleed_position_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'no_trim'}</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'no_trim'}</t>
+          <t>bleed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>finish_choices</t>
+          <t>bleed_position_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'matte'}</t>
+          <t>no_bleed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'matte'}</t>
+          <t>no bleed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>finish_choices</t>
+          <t>trim_position_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'glossy'}</t>
+          <t>trim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'glossy'}</t>
+          <t>trim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>finish_choices</t>
+          <t>trim_position_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'matte'}</t>
+          <t>no_trim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'matte'}</t>
+          <t>no trim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>paper_type_choices</t>
+          <t>file_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'card'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'card'}</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>paper_type_choices</t>
+          <t>file_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'card'}</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'card'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>paper_type_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'8pt'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': '8pt'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>bleed_position_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_'bleed'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 'bleed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>bleed_position_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'no_bleed'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'no_bleed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>trim_position_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'trim'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'trim'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>trim_position_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'no_trim'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'no_trim'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>file_type_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'pdf'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'pdf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>file_type_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'pdf'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'pdf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>file_type_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_'eps'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 'eps'}</t>
+          <t>eps</t>
         </is>
       </c>
     </row>
